--- a/data/trans_camb/IP1014-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Edad-trans_camb.xlsx
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-2,91; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,34; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,58</t>
+          <t>-0,5; 1,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,08</t>
+          <t>-1,08; 1,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,57</t>
+          <t>-1,11; 0,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,89</t>
+          <t>-0,49; 0,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,31</t>
+          <t>-0,92; 0,18</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,19; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,74</t>
+          <t>-1,03; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,32</t>
+          <t>-1,11; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,88</t>
+          <t>-0,54; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,73</t>
+          <t>-0,76; 0,62</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,43</t>
+          <t>-0,31; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,46</t>
+          <t>-0,16; 1,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,53</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,55; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,74</t>
+          <t>-0,48; 0,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,28</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,46</t>
+          <t>-0,21; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 393,76</t>
+          <t>-65,31; 392,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 223,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 341,17</t>
+          <t>-59,76; 329,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,91</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Edad-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-2,91; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,0</t>
+          <t>-3,34; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,0</t>
+          <t>-1,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,54</t>
+          <t>-0,38; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,52; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,05</t>
+          <t>-1,07; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,56</t>
+          <t>-1,09; 0,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,93</t>
+          <t>-0,53; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,18</t>
+          <t>-0,8; 0,2</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,19; —</t>
+          <t>-100,0; 684,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,72</t>
+          <t>-1,01; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,37</t>
+          <t>-1,25; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,87</t>
+          <t>-0,55; 1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,62</t>
+          <t>-0,67; 0,68</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,49</t>
+          <t>-0,31; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,24</t>
+          <t>-0,16; 1,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-0,8; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,74</t>
+          <t>-0,44; 0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,86; 0,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,48</t>
+          <t>-0,2; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,09</t>
+          <t>-0,45; 0,12</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 392,31</t>
+          <t>-67,96; 474,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,56</t>
+          <t>-100,0; 206,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 329,97</t>
+          <t>-55,86; 368,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 234,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,7</t>
+          <t>-1,09; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,0</t>
+          <t>-1,1; 0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,09</t>
+          <t>-0,39; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,82</t>
+          <t>-1,03; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,91</t>
+          <t>-0,51; 0,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,2</t>
+          <t>-0,79; 0,31</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-48,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>125,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-48,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 684,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,02; 1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,19; 1,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,05</t>
+          <t>-0,75; 0,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,68</t>
+          <t>-0,69; 0,73</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79,03%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,3; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,52; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,31</t>
+          <t>-0,14; 1,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>239,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>239,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,47; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,0</t>
+          <t>-0,75; 0,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,79</t>
+          <t>-0,16; 0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,24</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,54</t>
+          <t>-0,26; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,12</t>
+          <t>-0,48; 0,09</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,06%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>100,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-43,06%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,48; 393,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 474,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 368,82</t>
+          <t>-55,95; 341,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,5</t>
+          <t>-100,0; 105,91</t>
         </is>
       </c>
     </row>
